--- a/src/test/java/TestData/TestData_HeroKu.xlsx
+++ b/src/test/java/TestData/TestData_HeroKu.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MaheshStudy\StudySeleniumConcepts\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E964627-4CA9-461D-9FA7-B8CF49125552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462BCBD8-E848-4EEB-99C7-18B0E0FCE6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASIC_AUTH" sheetId="1" r:id="rId1"/>
+    <sheet name="CHALLENGING_DOM" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -24,8 +25,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Mahesh</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{E6C48F8D-60F2-42CA-B703-316FF90E75BB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Mahesh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+This is the linkText value associated with edit/delete elements on table and used as is in test logic</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>UserName</t>
   </si>
@@ -40,13 +75,34 @@
   </si>
   <si>
     <t>Congratulations! You must have the proper credentials.</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>FindText</t>
+  </si>
+  <si>
+    <t>Adipisci1</t>
+  </si>
+  <si>
+    <t>Definiebas6</t>
+  </si>
+  <si>
+    <t>WeeeeeDDD</t>
+  </si>
+  <si>
+    <t>edit</t>
+  </si>
+  <si>
+    <t>delete</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,6 +117,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -421,4 +490,51 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A07F8E3C-55A9-40A4-8BED-5A96A6DFD857}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>